--- a/addons/TinyTools/ConfigGenerator/TuningConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/TuningConfig.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="2" min="1" max="1"/>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>第 1 层的普通波数（用户口径'起始要刷 5 波普通敌人才打层主'）</t>
+          <t>第 1 层的普通波数（2026-10-17 用户要求全体 -1：5 -&gt; 4）</t>
         </is>
       </c>
     </row>
@@ -3061,6 +3061,99 @@
       <c r="G84" t="inlineStr">
         <is>
           <t>每携带 1 个召唤类武学，所属侠客最大生命 −本值（叠加：N 个 = N×本值）。锁死部分记入 BattleUnit.LockedHp，血条 UI 以银灰色显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MatTierEveryLayer</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>10</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>我自拟</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>每多少层一个材料品阶档（10 → 层 1~10 为凡铁）。[PLACEHOLDER]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MatMobDrop</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>我自拟</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>每次普通击杀掉落的材料数（确定性）。[PLACEHOLDER]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MatClearBonus</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>我自拟</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>打穿整层（收尾波获胜）额外奖励。 [PLACEHOLDER]</t>
         </is>
       </c>
     </row>

--- a/addons/TinyTools/ConfigGenerator/TuningConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/TuningConfig.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="2" min="1" max="1"/>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>叠毒每 2s 一跳</t>
+          <t>叠毒每秒一跳；层数不衰减（持久型 DoT）—— 2026-10-22 用户口径</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>灼烧吃来源 EffAtk 的 15%/跳</t>
+          <t>灼烧初值 = 来源 EffAtk 的 25%/跳（高于毒单层 20%），代价是逐跳衰减 —— 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3154,6 +3154,161 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>打穿整层（收尾波获胜）额外奖励。 [PLACEHOLDER]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BurnDecayPerTick</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>异常状态</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>用户口径</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>灼烧每跳后当前值 ×(1−本值) → 高开低走的爆发型 DoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BurnMinValue</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>异常状态</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>用户口径</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>灼烧当前值衰减到不足本值即熄灭（避免 0.5 这类永远跳不完的残余）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HotTick</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>异常状态</t>
+        </is>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>用户口径</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>持续治疗（HoT）每 2s 一跳（比 DoT 慢一倍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HotDur</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>异常状态</t>
+        </is>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>用户口径</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>持续治疗持续秒数（配合 HotTick = 5 跳）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ShieldKeepCap</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>用户口径</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>护盾保持率硬上限：行动时至少泄漏 15%，防止护盾变第二血条 —— 2026-10-21</t>
         </is>
       </c>
     </row>

--- a/addons/TinyTools/ConfigGenerator/TuningConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/TuningConfig.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="2" min="1" max="1"/>
@@ -1206,15 +1206,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PoisonPerStack</t>
+          <t>BurnTick</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>每栈吃来源 EffAtk 的 20%</t>
+          <t>灼烧每 1s 一跳</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PoisonMaxStack</t>
+          <t>BurnDur</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>叠毒最大层数</t>
+          <t>灼烧持续（秒）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BurnTick</t>
+          <t>HeroLevelMax</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>异常状态</t>
+          <t>等级成长</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -1288,30 +1288,30 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>灼烧每 1s 一跳</t>
+          <t>侠客等级上限（用户定）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BurnRate</t>
+          <t>StdHp</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.25</v>
+        <v>1000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>异常状态</t>
+          <t>等级成长</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1319,30 +1319,30 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>灼烧初值 = 来源 EffAtk 的 25%/跳（高于毒单层 20%），代价是逐跳衰减 —— 2026-10-22</t>
+          <t>标准轴：HP 基准（用户定）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BurnDur</t>
+          <t>StdHpGrowth</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>异常状态</t>
+          <t>等级成长</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1350,26 +1350,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>灼烧持续（秒）</t>
+          <t>标准轴：HP 每级增量（用户定）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HeroLevelMax</t>
+          <t>StdAtk</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>侠客等级上限（用户定）</t>
+          <t>标准轴：ATK 基准（用户定，v4.4 由 50 上调）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>StdHp</t>
+          <t>StdAtkGrowth</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1417,21 +1417,21 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>标准轴：HP 基准（用户定）</t>
+          <t>标准轴：ATK 每级增量（用户定）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>StdHpGrowth</t>
+          <t>StdDef</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100</v>
+        <v>7.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1448,21 +1448,21 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>标准轴：HP 每级增量（用户定）</t>
+          <t>标准轴：DEF 基准 = 原口径 30 × 0.25（**折表后**；30 是用户定的，0.25 是我按探针校准结果换算的）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>StdAtk</t>
+          <t>StdDefGrowth</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>标准轴：ATK 基准（用户定，v4.4 由 50 上调）</t>
+          <t>标准轴：DEF 每级增量 = 原口径 2 × 0.25（折表后）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>StdAtkGrowth</t>
+          <t>StdSpd</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>标准轴：ATK 每级增量（用户定）</t>
+          <t>标准轴：SPD 50（速度占模的基准，不随等级成长）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>StdDef</t>
+          <t>SummonCap</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>等级成长</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -1536,30 +1536,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>标准轴：DEF 基准 = 原口径 30 × 0.25（**折表后**；30 是用户定的，0.25 是我按探针校准结果换算的）</t>
+          <t>全队召唤位上限（用户口径'提高'，值由我取 4→8）。外层闸；内层还有类型档位与武学覆盖</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>StdDefGrowth</t>
+          <t>SummonTtl</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>等级成长</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -1567,30 +1567,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>标准轴：DEF 每级增量 = 原口径 2 × 0.25（折表后）</t>
+          <t>召唤物默认存在时间（秒）；SummonConfig.Ttl 可覆盖</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>StdSpd</t>
+          <t>SummonAoeDr</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>等级成长</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -1598,30 +1598,30 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>标准轴：SPD 50（速度占模的基准，不随等级成长）</t>
+          <t>召唤物受群体伤害减伤（用户报'召唤物被一个 AoE 刮死'后我取 0.5）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SummonCap</t>
+          <t>BossEvery</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>推图</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -1634,25 +1634,25 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>全队召唤位上限（用户口径'提高'，值由我取 4→8）。外层闸；内层还有类型档位与武学覆盖</t>
+          <t>每 10 层一个层主（用户口径'每10层'）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SummonTtl</t>
+          <t>WaveSize</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>推图</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -1660,30 +1660,30 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>召唤物默认存在时间（秒）；SummonConfig.Ttl 可覆盖</t>
+          <t>每波敌方单位数（用户口径'每波4个'；与玩家 4 人对称）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SummonAoeDr</t>
+          <t>RetryEvery</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>推图</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -1691,26 +1691,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>用户口径</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>召唤物受群体伤害减伤（用户报'召唤物被一个 AoE 刮死'后我取 0.5）</t>
+          <t>挂机模式下每刷多少场自动重试上一层一次（0=只手动）</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BossEvery</t>
+          <t>FirstMobWaves</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1722,26 +1722,26 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>用户口径</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>每 10 层一个层主（用户口径'每10层'）</t>
+          <t>第 1 层的普通波数（2026-10-17 用户要求全体 -1：5 -&gt; 4）</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WaveSize</t>
+          <t>WaveStepEvery</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>用户口径</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>每波敌方单位数（用户口径'每波4个'；与玩家 4 人对称）</t>
+          <t>每多少层普通波数 +1（用户口径'每 10 层加 1 波'）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RetryEvery</t>
+          <t>WaveHealRatio</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1784,30 +1784,30 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>挂机模式下每刷多少场自动重试上一层一次（0=只手动）</t>
+          <t>波间恢复比例（用户口径'每波敌人间只恢复 10% 的血量'）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FirstMobWaves</t>
+          <t>KillGainC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>推图</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -1815,30 +1815,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>第 1 层的普通波数（2026-10-17 用户要求全体 -1：5 -&gt; 4）</t>
+          <t>每次击杀的修为（=经验）。用户口径'击杀即时掉落'；值我取 0.5，使一层 4 杀合计 = 原 2.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WaveStepEvery</t>
+          <t>GainA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>1.16</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>推图</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -1846,30 +1846,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>每多少层普通波数 +1（用户口径'每 10 层加 1 波'）</t>
+          <t>修为掉落底数（框架 §4：与敌方 HP 同底数 1.16）。2026-10-16 用户口径"层级高的产出也提高"→ 核查后确认**本就在随层涨**，**不改**</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WaveHealRatio</t>
+          <t>KillSilverC</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>推图</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -1877,26 +1877,26 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>波间恢复比例（用户口径'每波敌人间只恢复 10% 的血量'）</t>
+          <t>每次击杀的银两。我取 2.5，使一层 4 杀合计 = 10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KillGainC</t>
+          <t>SilverA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5</v>
+        <v>1.16</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1908,26 +1908,26 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>用户口径</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>每次击杀的修为（=经验）。用户口径'击杀即时掉落'；值我取 0.5，使一层 4 杀合计 = 原 2.0</t>
+          <t>银两掉落底数（框架 §4：同 1.16）。同 GainA，**不改**</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GainA</t>
+          <t>LevelBase</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.16</v>
+        <v>30</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1939,26 +1939,26 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>修为掉落底数（框架 §4：与敌方 HP 同底数 1.16）。2026-10-16 用户口径"层级高的产出也提高"→ 核查后确认**本就在随层涨**，**不改**</t>
+          <t>升 L1→L2 所需修为（[PLACEHOLDER]）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KillSilverC</t>
+          <t>LevelD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1970,26 +1970,26 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>每次击杀的银两。我取 2.5，使一层 4 杀合计 = 10</t>
+          <t>升级成本底数（框架 §4：必须略大于 GainA，消费涨得比产出快）</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SilverA</t>
+          <t>MaxLevel</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.16</v>
+        <v>40</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2001,30 +2001,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>银两掉落底数（框架 §4：同 1.16）。同 GainA，**不改**</t>
+          <t>等级上限（与 HeroLevelMax 同义，用户定）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LevelBase</t>
+          <t>StarStep</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>客栈资质</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -2032,30 +2032,30 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>升 L1→L2 所需修为（[PLACEHOLDER]）</t>
+          <t>星级乘数：★1=×1.0，每星 +15%（《侠客与资质》§二）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LevelD</t>
+          <t>StarW1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.18</v>
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>客栈资质</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -2068,25 +2068,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>升级成本底数（框架 §4：必须略大于 GainA，消费涨得比产出快）</t>
+          <t>★1 概率(%): 50/30/12/6/2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MaxLevel</t>
+          <t>StarW2</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>客栈资质</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -2094,26 +2094,26 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>等级上限（与 HeroLevelMax 同义，用户定）</t>
+          <t>★2 概率(%)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>StarStep</t>
+          <t>StarW3</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.15</v>
+        <v>12</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2130,21 +2130,21 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>星级乘数：★1=×1.0，每星 +15%（《侠客与资质》§二）</t>
+          <t>★3 概率(%)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>StarW1</t>
+          <t>StarW4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>★1 概率(%): 50/30/12/6/2</t>
+          <t>★4 概率(%)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>StarW2</t>
+          <t>StarW5</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2192,21 +2192,21 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>★2 概率(%)</t>
+          <t>★5 概率(%)（制造'客栈刷屏时刻'）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>StarW3</t>
+          <t>StatRollMin</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>-20</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>★3 概率(%)</t>
+          <t>成长率下限(%)：三维各自独立、均匀掷 −20~+30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>StarW4</t>
+          <t>StatRollMax</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>★4 概率(%)</t>
+          <t>成长率上限(%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>StarW5</t>
+          <t>AffixW0</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2285,21 +2285,21 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>★5 概率(%)（制造'客栈刷屏时刻'）</t>
+          <t>词条 0 个概率(%): 40/45/15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>StatRollMin</t>
+          <t>AffixW1</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-20</v>
+        <v>45</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>成长率下限(%)：三维各自独立、均匀掷 −20~+30</t>
+          <t>词条 1 个概率(%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>StatRollMax</t>
+          <t>AffixW2</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2347,21 +2347,21 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>成长率上限(%)</t>
+          <t>词条 2 个概率(%)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AffixW0</t>
+          <t>InnSlots</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>词条 0 个概率(%): 40/45/15</t>
+          <t>客栈栏位数（默认 4；天赋树'客栈扩建'可 +1）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AffixW1</t>
+          <t>InnFreeRefresh</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>词条 1 个概率(%)</t>
+          <t>每世免费手动刷新次数</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AffixW2</t>
+          <t>InnRefreshBase</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2435,26 +2435,26 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>词条 2 个概率(%)</t>
+          <t>手动刷新基础价（**银两**）[我自拟 · PLACEHOLDER 待定价]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>InnSlots</t>
+          <t>InnRefreshGrowth</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2466,26 +2466,26 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>客栈栏位数（默认 4；天赋树'客栈扩建'可 +1）</t>
+          <t>付费刷新价格递增倍率 [我自拟 · PLACEHOLDER]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>InnFreeRefresh</t>
+          <t>RecruitBase</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2497,26 +2497,26 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>每世免费手动刷新次数</t>
+          <t>招募基础价（**银两**；文档写'修为'，因修为=经验已改口径）[我自拟 · PLACEHOLDER]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>InnRefreshBase</t>
+          <t>StarCostStep</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2528,26 +2528,26 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>手动刷新基础价（**银两**）[我自拟 · PLACEHOLDER 待定价]</t>
+          <t>星级费阶：费用系数 = 1+(星−1)×本值（★1=1×、★5=5×）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>InnRefreshGrowth</t>
+          <t>RosterSize</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2559,34 +2559,34 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>文档规定</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>付费刷新价格递增倍率 [我自拟 · PLACEHOLDER]</t>
+          <t>编队人数上限（与战斗编制 4 人一致）</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RecruitBase</t>
+          <t>SPD_COEF</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30</v>
+        <v>0.6</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>客栈资质</t>
+          <t>构建期</t>
         </is>
       </c>
       <c r="E69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2595,79 +2595,79 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>招募基础价（**银两**；文档写'修为'，因修为=经验已改口径）[我自拟 · PLACEHOLDER]</t>
+          <t>速度占模系数：occ = clamp(1−0.6×(SPD−50)/50, …)。用户只说'要考虑速度影响'，系数我取</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>StarCostStep</t>
+          <t>OCC_MIN</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>客栈资质</t>
+          <t>构建期</t>
         </is>
       </c>
       <c r="E70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>星级费阶：费用系数 = 1+(星−1)×本值（★1=1×、★5=5×）</t>
+          <t>速度占模下限</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RosterSize</t>
+          <t>OCC_MAX</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>客栈资质</t>
+          <t>构建期</t>
         </is>
       </c>
       <c r="E71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>文档规定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>编队人数上限（与战斗编制 4 人一致）</t>
+          <t>速度占模上限</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPD_COEF</t>
+          <t>B_RANGE_LO</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2683,26 +2683,26 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>速度占模系数：occ = clamp(1−0.6×(SPD−50)/50, …)。用户只说'要考虑速度影响'，系数我取</t>
+          <t>基础随机下限（用户口径 ±40%）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OCC_MIN</t>
+          <t>B_RANGE_HI</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2714,26 +2714,26 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>速度占模下限</t>
+          <t>基础随机上限（用户口径 ±40%）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OCC_MAX</t>
+          <t>G_RANGE_LO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2745,26 +2745,26 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>速度占模上限</t>
+          <t>成长随机下限（用户口径 ±20%）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B_RANGE_LO</t>
+          <t>G_RANGE_HI</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>基础随机下限（用户口径 ±40%）</t>
+          <t>成长随机上限（用户口径 ±20%）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B_RANGE_HI</t>
+          <t>N_RUNS</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>基础随机上限（用户口径 ±40%）</t>
+          <t>随机跑多少次取最均衡（用户口径'随机跑10次'）</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>G_RANGE_LO</t>
+          <t>ENEMY_MOB_BUFF</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2838,26 +2838,26 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>成长随机下限（用户口径 ±20%）</t>
+          <t>普通敌人基础属性上调（用户口径'略微提高'，值我取 ×1.10）；已落 EnemyConfig 表</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>G_RANGE_HI</t>
+          <t>ELITE_HP_MUL</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2869,26 +2869,26 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>成长随机上限（用户口径 ±20%）</t>
+          <t>精英 = 同档杂兵 ×2.0 HP；已落 EnemyConfig 表</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N_RUNS</t>
+          <t>ELITE_ATK_MUL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2900,26 +2900,26 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>随机跑多少次取最均衡（用户口径'随机跑10次'）</t>
+          <t>精英 = 同档杂兵 ×1.3 ATK；已落 EnemyConfig 表</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ENEMY_MOB_BUFF</t>
+          <t>ELITE_DEF_MUL</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2931,65 +2931,65 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>用户口径</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>普通敌人基础属性上调（用户口径'略微提高'，值我取 ×1.10）；已落 EnemyConfig 表</t>
+          <t>精英 = 同档杂兵 ×1.3 DEF；已落 EnemyConfig 表</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ELITE_HP_MUL</t>
+          <t>SummonHpPenaltyPerSkill</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>0.15</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>构建期</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户指定</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>精英 = 同档杂兵 ×2.0 HP；已落 EnemyConfig 表</t>
+          <t>每携带 1 个召唤类武学，所属侠客最大生命 −本值（叠加：N 个 = N×本值）。锁死部分记入 BattleUnit.LockedHp，血条 UI 以银灰色显示</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ELITE_ATK_MUL</t>
+          <t>MatTierEveryLayer</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>构建期</t>
+          <t>材料</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2998,29 +2998,29 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>精英 = 同档杂兵 ×1.3 ATK；已落 EnemyConfig 表</t>
+          <t>每多少层一个材料品阶档（10 → 层 1~10 为凡铁）。[PLACEHOLDER]</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ELITE_DEF_MUL</t>
+          <t>MatMobDrop</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>构建期</t>
+          <t>材料</t>
         </is>
       </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3029,25 +3029,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>精英 = 同档杂兵 ×1.3 DEF；已落 EnemyConfig 表</t>
+          <t>每次普通击杀掉落的材料数（确定性）。[PLACEHOLDER]</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SummonHpPenaltyPerSkill</t>
+          <t>MatClearBonus</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.15</v>
+        <v>5</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>材料</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3055,30 +3055,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>用户指定</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>每携带 1 个召唤类武学，所属侠客最大生命 −本值（叠加：N 个 = N×本值）。锁死部分记入 BattleUnit.LockedHp，血条 UI 以银灰色显示</t>
+          <t>打穿整层（收尾波获胜）额外奖励。 [PLACEHOLDER]</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MatTierEveryLayer</t>
+          <t>HotTick</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>异常状态</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3086,30 +3086,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>每多少层一个材料品阶档（10 → 层 1~10 为凡铁）。[PLACEHOLDER]</t>
+          <t>持续治疗（HoT）每 2s 一跳（比 DoT 慢一倍）</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MatMobDrop</t>
+          <t>HotDur</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>异常状态</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3117,30 +3117,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>每次普通击杀掉落的材料数（确定性）。[PLACEHOLDER]</t>
+          <t>持续治疗持续秒数（配合 HotTick = 5 跳）</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MatClearBonus</t>
+          <t>ShieldKeepCap</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>0.85</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>护盾</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -3148,30 +3148,30 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>我自拟</t>
+          <t>用户口径</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>打穿整层（收尾波获胜）额外奖励。 [PLACEHOLDER]</t>
+          <t>护盾保持率硬上限：行动时至少泄漏 15%，防止护盾变第二血条 —— 2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BurnDecayPerTick</t>
+          <t>MissingHpFloor</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>异常状态</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>用户口径</t>
+          <t>我自拟</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>灼烧每跳后当前值 ×(1−本值) → 高开低走的爆发型 DoT</t>
+          <t>斩杀（MissingHp）保底：满血目标已损=0 时按 攻击×本值 打一记，避免空放。刻意压低，防止它变成通用伤害卡 —— 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BurnMinValue</t>
+          <t>PoisonPerStackDmg</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -3215,21 +3215,21 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>灼烧当前值衰减到不足本值即熄灭（避免 0.5 这类永远跳不完的残余）</t>
+          <t>毒：每层每跳 **1 点**（固定点数，不随等级/目标气血变化），强度只靠每次施加层数调 —— 2026-10-23 用户口径「每层每跳都是 1 点，好计算」</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HotTick</t>
+          <t>BurnPerStackDmg</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>持续治疗（HoT）每 2s 一跳（比 DoT 慢一倍）</t>
+          <t>火：每层每跳 **1 点**（与毒同价），代价是被护盾吸收 + 只有 10s，所以每次施加层数 = 毒的 ×1.5 —— 2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HotDur</t>
+          <t>HotPerStackHeal</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3277,25 +3277,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>持续治疗持续秒数（配合 HotTick = 5 跳）</t>
+          <t>HoT：每层每跳回 **1 点**（2s 一跳）—— 2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ShieldKeepCap</t>
+          <t>PoisonWeakenPerHeal</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>异常状态</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3308,7 +3308,69 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>护盾保持率硬上限：行动时至少泄漏 15%，防止护盾变第二血条 —— 2026-10-21</t>
+          <t>每次实际回血的治疗让毒层 −5%，最少留 1 层；HoT 不触发 —— 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>96</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BurnPierceShield</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>异常状态</t>
+        </is>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>用户口径</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>火是否无视护盾：0=被护盾吸收（默认，毒才是破坦手段）；1=和毒一样穿透 —— 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>97</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BreakBonus</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>异常状态</t>
+        </is>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>我自拟</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>破绽每层：那一次受击的伤害 ×(1+本值)；每次施加 +1 层、每挨一刀消耗一层（一次行动只吃一层），层数不设上限 —— 2026-10-24 用户口径「只持续到下次受击 + 允许叠层」</t>
         </is>
       </c>
     </row>
